--- a/administrative_forms/006_team_bonding_session_planning_form--administrative_forms.xlsx
+++ b/administrative_forms/006_team_bonding_session_planning_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -940,46 +940,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>food_preferences_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'jane'}</t>
+          <t>food_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Jane'}</t>
+          <t>Food A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>food_preferences_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'john'}</t>
+          <t>food_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'John'}</t>
+          <t>Food B</t>
         </is>
       </c>
     </row>
@@ -991,46 +991,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'food_a'}</t>
+          <t>food_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Food A'}</t>
+          <t>Food C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>food_preferences_choices</t>
+          <t>activities_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'food_b'}</t>
+          <t>activity_a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Food B'}</t>
+          <t>Activity A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>food_preferences_choices</t>
+          <t>activities_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'food_c'}</t>
+          <t>activity_b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Food C'}</t>
+          <t>Activity B</t>
         </is>
       </c>
     </row>
@@ -1042,46 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'activity_a'}</t>
+          <t>activity_c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Activity A'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>activities_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'activity_b'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Activity B'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>activities_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'activity_c'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Activity C'}</t>
+          <t>Activity C</t>
         </is>
       </c>
     </row>
